--- a/InputData/trans/BRASC/BAU Rng Anxiety Shadow Costs.xlsx
+++ b/InputData/trans/BRASC/BAU Rng Anxiety Shadow Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BRASC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BRASC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC5A8D2-E691-41E9-9DAC-BAC2BF86E64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB37FF9-DC7A-43A7-A458-56F2E308DCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="BRASC" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="income">Calculations!#REF!</definedName>
-    <definedName name="Range_EV">Calculations!#REF!</definedName>
-    <definedName name="range_ICE">Calculations!#REF!</definedName>
+    <definedName name="income">Calculations!$B$10</definedName>
+    <definedName name="Range_EV">Calculations!$B$9</definedName>
+    <definedName name="range_ICE">Calculations!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>Source:</t>
   </si>
@@ -107,15 +107,24 @@
     <t>cv (thousand USD)</t>
   </si>
   <si>
+    <t>https://www.census.gov/library/publications/2020/demo/p60-270.html</t>
+  </si>
+  <si>
     <t>Median US Income</t>
   </si>
   <si>
     <t>United States Census Bureau</t>
   </si>
   <si>
+    <t>Income and Poverty in the United States: 2019</t>
+  </si>
+  <si>
     <t>First bullet of "Highlights"</t>
   </si>
   <si>
+    <t>2019 to 2012 USD</t>
+  </si>
+  <si>
     <t>Range and Fueling Availability 'Costs'</t>
   </si>
   <si>
@@ -128,9 +137,30 @@
     <t>Gasoline vehicle range</t>
   </si>
   <si>
+    <t>All-Electric Vehicle Ranges Can Exceed Those of Some Gasoline Vehicles</t>
+  </si>
+  <si>
+    <t>https://www.energy.gov/eere/vehicles/fact-939-august-22-2016-all-electric-vehicle-ranges-can-exceed-those-some-gasoline</t>
+  </si>
+  <si>
+    <t>First Figure</t>
+  </si>
+  <si>
     <t>median range ice (hundred miles)</t>
   </si>
   <si>
+    <t>Inside Evs</t>
+  </si>
+  <si>
+    <t>The Median Range of Fully Electric Vehicles Exceeded 250 Miles in 2020</t>
+  </si>
+  <si>
+    <t>https://insideevs.com/news/464449/median-range-evs-2020-exceeded-250-miles/</t>
+  </si>
+  <si>
+    <t>EV range</t>
+  </si>
+  <si>
     <t>In the US, we use a DOE study to calculate a Range Compensating Value and a Fuel Availability Value.</t>
   </si>
   <si>
@@ -146,34 +176,16 @@
     <t xml:space="preserve">250 miles and is forecated to continue improving. Therefore, we start with today's median range, and assume </t>
   </si>
   <si>
+    <t>the range will reach 300 miles by 2050.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*2020 median range taken from historical data. 2030 and 2050 are estimated, with the 2050 </t>
+  </si>
+  <si>
+    <t>range roughly corresponding to today's maximum range</t>
+  </si>
+  <si>
     <t>BRAaCTSC BAU Range Anxiety Shadow Cost</t>
-  </si>
-  <si>
-    <t>2024 EV range</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/eere/vehicles/articles/fotw-1375-december-30-2024-median-ev-range-model-year-2024-reached-record</t>
-  </si>
-  <si>
-    <t>FOTW #1375, December 30, 2024: Median EV Range in Model Year 2024 Reached a Record High of 283 Miles per Charge</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/eere/vehicles/articles/fotw-1221-january-17-2022-model-year-2021-all-electric-vehicles-had-median</t>
-  </si>
-  <si>
-    <t>FOTW #1221, January 17, 2022: Model Year 2021 All-Electric Vehicles Had a Median Driving Range about 60% That of Gasoline Powered Vehicles</t>
-  </si>
-  <si>
-    <t>the range will reach the equivalent of a gasoline vehicle (eliminating range anxiety) by 2050.</t>
-  </si>
-  <si>
-    <t>2024 to 2012 USD</t>
-  </si>
-  <si>
-    <t>https://www.census.gov/library/publications/2025/demo/p60-286.html</t>
-  </si>
-  <si>
-    <t>Income in the United States: 2024</t>
   </si>
 </sst>
 </file>
@@ -548,199 +560,207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="7">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="7">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="7">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="7">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37">
-        <v>0.73199999999999998</v>
+      <c r="B38">
+        <v>0.89805481563188172</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B26" r:id="rId1" xr:uid="{14EF0A86-0973-41E2-9D23-51C96C77958E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" customWidth="1"/>
-    <col min="2" max="2" width="26.453125" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -748,12 +768,12 @@
         <v>-0.36099999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -761,7 +781,7 @@
         <v>1.268</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -769,60 +789,86 @@
         <v>-0.11600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C7">
+        <v>2030</v>
+      </c>
+      <c r="D7">
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="C8">
+        <v>4.12</v>
+      </c>
+      <c r="D8">
         <f>B8</f>
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9">
-        <v>2.83</v>
+      <c r="B9">
+        <v>2.59</v>
       </c>
       <c r="C9" s="9">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10">
-        <f>83730/1000*About!B37</f>
-        <v>61.29036</v>
+        <v>68.703000000000003</v>
       </c>
       <c r="C10" s="9">
+        <f>income</f>
+        <v>68.703000000000003</v>
+      </c>
+      <c r="D10" s="9">
         <f>B10</f>
-        <v>61.29036</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>68.703000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5">
-        <f>($B$4/$B$2*B9*(1-B8/B9)+$B$5/$B$2*B9^2*(1-B8^2/B9^2))*LN(B10)*About!$B$37</f>
-        <v>4.7291537731134952</v>
-      </c>
-      <c r="C12" s="5">
-        <f>($B$4/$B$2*C9*(1-C8/C9)+$B$5/$B$2*C9^2*(1-C8^2/C9^2))*LN(C10)*About!$B$37</f>
+      <c r="B14" s="5">
+        <f>($B$4/$B$2*B9*(1-B8/B9)+$B$5/$B$2*B9^2*(1-B8^2/B9^2))*LN(income)*About!$B$38</f>
+        <v>7.8828464065137096</v>
+      </c>
+      <c r="C14" s="5">
+        <f>($B$4/$B$2*C9*(1-C8/C9)+$B$5/$B$2*C9^2*(1-C8^2/C9^2))*LN(income)*About!$B$38</f>
+        <v>5.2099509525186276</v>
+      </c>
+      <c r="D14" s="5">
+        <f>($B$4/$B$2*D9*(1-D8/D9)+$B$5/$B$2*D9^2*(1-D8^2/D9^2))*LN(income)*About!$B$38</f>
         <v>0</v>
       </c>
     </row>
@@ -837,211 +883,239 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AG2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="4">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="4">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="D1" s="4">
+      <c r="H1" s="4">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="F1" s="4">
+      <c r="J1" s="4">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="H1" s="4">
+      <c r="L1" s="4">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="J1" s="4">
+      <c r="N1" s="4">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="L1" s="4">
+      <c r="P1" s="4">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="N1" s="4">
+      <c r="R1" s="4">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="P1" s="4">
+      <c r="T1" s="4">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="R1" s="4">
+      <c r="V1" s="4">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="T1" s="4">
+      <c r="X1" s="4">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="V1" s="4">
+      <c r="Z1" s="4">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="X1" s="4">
+      <c r="AB1" s="4">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="Z1" s="4">
+      <c r="AD1" s="4">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AB1" s="4">
+      <c r="AF1" s="4">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!B1)*1000</f>
-        <v>4729.1537731134667</v>
+        <f t="array" ref="B2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,B1)*1000*About!$B$38</f>
+        <v>7079.2281762560442</v>
       </c>
       <c r="C2" s="3" cm="1">
-        <f t="array" ref="C2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!C1)*1000</f>
-        <v>4547.2632433783247</v>
+        <f t="array" ref="C2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,C1)*1000*About!$B$38</f>
+        <v>6839.1875128420379</v>
       </c>
       <c r="D2" s="3" cm="1">
-        <f t="array" ref="D2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!D1)*1000</f>
-        <v>4365.3727136431826</v>
+        <f t="array" ref="D2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,D1)*1000*About!$B$38</f>
+        <v>6599.1468494279288</v>
       </c>
       <c r="E2" s="3" cm="1">
-        <f t="array" ref="E2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!E1)*1000</f>
-        <v>4183.4821839080405</v>
+        <f t="array" ref="E2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,E1)*1000*About!$B$38</f>
+        <v>6359.1061860138198</v>
       </c>
       <c r="F2" s="3" cm="1">
-        <f t="array" ref="F2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!F1)*1000</f>
-        <v>4001.5916541728984</v>
+        <f t="array" ref="F2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,F1)*1000*About!$B$38</f>
+        <v>6119.0655225997107</v>
       </c>
       <c r="G2" s="3" cm="1">
-        <f t="array" ref="G2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!G1)*1000</f>
-        <v>3819.7011244377563</v>
+        <f t="array" ref="G2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,G1)*1000*About!$B$38</f>
+        <v>5879.0248591857035</v>
       </c>
       <c r="H2" s="3" cm="1">
-        <f t="array" ref="H2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!H1)*1000</f>
-        <v>3637.8105947026711</v>
+        <f t="array" ref="H2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,H1)*1000*About!$B$38</f>
+        <v>5638.9841957715944</v>
       </c>
       <c r="I2" s="3" cm="1">
-        <f t="array" ref="I2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!I1)*1000</f>
-        <v>3455.920064967529</v>
+        <f t="array" ref="I2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,I1)*1000*About!$B$38</f>
+        <v>5398.9435323574853</v>
       </c>
       <c r="J2" s="3" cm="1">
-        <f t="array" ref="J2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!J1)*1000</f>
-        <v>3274.0295352323869</v>
+        <f t="array" ref="J2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,J1)*1000*About!$B$38</f>
+        <v>5158.9028689433762</v>
       </c>
       <c r="K2" s="3" cm="1">
-        <f t="array" ref="K2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!K1)*1000</f>
-        <v>3092.1390054972449</v>
+        <f t="array" ref="K2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,K1)*1000*About!$B$38</f>
+        <v>4918.8622055292672</v>
       </c>
       <c r="L2" s="3" cm="1">
-        <f t="array" ref="L2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!L1)*1000</f>
-        <v>2910.2484757621028</v>
+        <f t="array" ref="L2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,L1)*1000*About!$B$38</f>
+        <v>4678.8215421152599</v>
       </c>
       <c r="M2" s="3" cm="1">
-        <f t="array" ref="M2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!M1)*1000</f>
-        <v>2728.3579460269607</v>
+        <f t="array" ref="M2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,M1)*1000*About!$B$38</f>
+        <v>4444.8804650095735</v>
       </c>
       <c r="N2" s="3" cm="1">
-        <f t="array" ref="N2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!N1)*1000</f>
-        <v>2546.4674162918186</v>
+        <f t="array" ref="N2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,N1)*1000*About!$B$38</f>
+        <v>4210.9393879037852</v>
       </c>
       <c r="O2" s="3" cm="1">
-        <f t="array" ref="O2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!O1)*1000</f>
-        <v>2364.5768865567334</v>
+        <f t="array" ref="O2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,O1)*1000*About!$B$38</f>
+        <v>3976.998310797997</v>
       </c>
       <c r="P2" s="3" cm="1">
-        <f t="array" ref="P2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!P1)*1000</f>
-        <v>2182.6863568215913</v>
+        <f t="array" ref="P2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,P1)*1000*About!$B$38</f>
+        <v>3743.0572336923101</v>
       </c>
       <c r="Q2" s="3" cm="1">
-        <f t="array" ref="Q2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!Q1)*1000</f>
-        <v>2000.7958270864492</v>
+        <f t="array" ref="Q2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Q1)*1000*About!$B$38</f>
+        <v>3509.1161565865218</v>
       </c>
       <c r="R2" s="3" cm="1">
-        <f t="array" ref="R2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!R1)*1000</f>
-        <v>1818.9052973513071</v>
+        <f t="array" ref="R2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,R1)*1000*About!$B$38</f>
+        <v>3275.1750794807331</v>
       </c>
       <c r="S2" s="3" cm="1">
-        <f t="array" ref="S2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!S1)*1000</f>
-        <v>1637.014767616165</v>
+        <f t="array" ref="S2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,S1)*1000*About!$B$38</f>
+        <v>3041.2340023749448</v>
       </c>
       <c r="T2" s="3" cm="1">
-        <f t="array" ref="T2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!T1)*1000</f>
-        <v>1455.124237881023</v>
+        <f t="array" ref="T2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,T1)*1000*About!$B$38</f>
+        <v>2807.2929252692584</v>
       </c>
       <c r="U2" s="3" cm="1">
-        <f t="array" ref="U2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!U1)*1000</f>
-        <v>1273.2337081458809</v>
+        <f t="array" ref="U2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,U1)*1000*About!$B$38</f>
+        <v>2573.3518481634696</v>
       </c>
       <c r="V2" s="3" cm="1">
-        <f t="array" ref="V2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!V1)*1000</f>
-        <v>1091.3431784107388</v>
+        <f t="array" ref="V2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,V1)*1000*About!$B$38</f>
+        <v>2339.4107710576814</v>
       </c>
       <c r="W2" s="3" cm="1">
-        <f t="array" ref="W2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!W1)*1000</f>
-        <v>909.45264867565356</v>
+        <f t="array" ref="W2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,W1)*1000*About!$B$38</f>
+        <v>2105.4696939518926</v>
       </c>
       <c r="X2" s="3" cm="1">
-        <f t="array" ref="X2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!X1)*1000</f>
-        <v>727.56211894051148</v>
+        <f t="array" ref="X2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,X1)*1000*About!$B$38</f>
+        <v>1871.5286168462062</v>
       </c>
       <c r="Y2" s="3" cm="1">
-        <f t="array" ref="Y2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!Y1)*1000</f>
-        <v>545.6715892053694</v>
+        <f t="array" ref="Y2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Y1)*1000*About!$B$38</f>
+        <v>1637.5875397404177</v>
       </c>
       <c r="Z2" s="3" cm="1">
-        <f t="array" ref="Z2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!Z1)*1000</f>
-        <v>363.78105947022732</v>
+        <f t="array" ref="Z2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Z1)*1000*About!$B$38</f>
+        <v>1403.6464626346292</v>
       </c>
       <c r="AA2" s="3" cm="1">
-        <f t="array" ref="AA2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!AA1)*1000</f>
-        <v>181.89052973508524</v>
+        <f t="array" ref="AA2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AA1)*1000*About!$B$38</f>
+        <v>1169.7053855288407</v>
       </c>
       <c r="AB2" s="3" cm="1">
-        <f t="array" ref="AB2">TREND(Calculations!$B$12:$C$12,Calculations!$B$7:$C$7,BRASC!AB1)*1000</f>
-        <v>-5.6843418860808015E-11</v>
-      </c>
-      <c r="AC2" s="3"/>
+        <f t="array" ref="AB2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AB1)*1000*About!$B$38</f>
+        <v>935.76430842315415</v>
+      </c>
+      <c r="AC2" s="3" cm="1">
+        <f t="array" ref="AC2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AC1)*1000*About!$B$38</f>
+        <v>701.82323131736564</v>
+      </c>
+      <c r="AD2" s="3" cm="1">
+        <f t="array" ref="AD2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AD1)*1000*About!$B$38</f>
+        <v>467.88215421157707</v>
+      </c>
+      <c r="AE2" s="3" cm="1">
+        <f t="array" ref="AE2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AE1)*1000*About!$B$38</f>
+        <v>233.94107710578854</v>
+      </c>
+      <c r="AF2" s="3" cm="1">
+        <f t="array" ref="AF2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AF1)*1000*About!$B$38</f>
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
